--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA116DC-9D8F-4CED-B852-9E7BEB0440AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0719BFAF-C805-4D4F-AE1B-3F0F2948E6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="nmos" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="77">
   <si>
     <t>Part Number</t>
   </si>
@@ -253,6 +253,21 @@
   </si>
   <si>
     <t>PNP 1B3C2E</t>
+  </si>
+  <si>
+    <t>AO3400</t>
+  </si>
+  <si>
+    <t>AO3400 SOT23</t>
+  </si>
+  <si>
+    <t>Hottech Semiconductor</t>
+  </si>
+  <si>
+    <t>AO3401A</t>
+  </si>
+  <si>
+    <t>AO3401A SOT23</t>
   </si>
 </sst>
 </file>
@@ -810,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A86DCBB-C7F7-4A7A-A3DD-2292F908D4B3}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -1079,6 +1094,29 @@
         <v>47</v>
       </c>
     </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1086,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A36DDB-75CB-4526-8B7C-3E1D54E638B5}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -1281,6 +1319,29 @@
       </c>
       <c r="G8" s="3" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0719BFAF-C805-4D4F-AE1B-3F0F2948E6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5052B024-D0DE-4BC2-A8D5-BD92C103EC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="nmos" sheetId="8" r:id="rId1"/>
@@ -1124,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A36DDB-75CB-4526-8B7C-3E1D54E638B5}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -1202,12 +1202,12 @@
       <c r="F3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1225,7 +1225,7 @@
       <c r="F4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1317,21 +1317,21 @@
       <c r="F8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>75</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>75</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -1341,8 +1341,11 @@
         <v>24</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>74</v>
-      </c>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5052B024-D0DE-4BC2-A8D5-BD92C103EC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A5ACF0-2D96-4EE9-93B4-4DADF9E1854F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="79">
   <si>
     <t>Part Number</t>
   </si>
@@ -268,6 +268,12 @@
   </si>
   <si>
     <t>AO3401A SOT23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STP24NF10 </t>
+  </si>
+  <si>
+    <t>STP24NF10  TO-263-2</t>
   </si>
 </sst>
 </file>
@@ -825,14 +831,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A86DCBB-C7F7-4A7A-A3DD-2292F908D4B3}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
     <col min="3" max="3" width="22.140625" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" customWidth="1"/>
     <col min="6" max="7" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1115,6 +1121,29 @@
       </c>
       <c r="G12" s="2" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A5ACF0-2D96-4EE9-93B4-4DADF9E1854F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945EEC05-769E-422D-AA85-4F2D83EADD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -270,10 +270,10 @@
     <t>AO3401A SOT23</t>
   </si>
   <si>
-    <t xml:space="preserve">STP24NF10 </t>
-  </si>
-  <si>
-    <t>STP24NF10  TO-263-2</t>
+    <t>STB24NF10</t>
+  </si>
+  <si>
+    <t>STB24NF10  TO-263-2</t>
   </si>
 </sst>
 </file>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945EEC05-769E-422D-AA85-4F2D83EADD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5009AFC0-E8F3-46FA-A787-DD981AB783EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="1770" yWindow="1770" windowWidth="23085" windowHeight="13635" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="nmos" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="93">
   <si>
     <t>Part Number</t>
   </si>
@@ -274,6 +274,49 @@
   </si>
   <si>
     <t>STB24NF10  TO-263-2</t>
+  </si>
+  <si>
+    <t>2П795А92</t>
+  </si>
+  <si>
+    <t>2П795А92 КТ-94</t>
+  </si>
+  <si>
+    <t>КТ-94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+АЕЯР.432140.273ТУ</t>
+  </si>
+  <si>
+    <t>2П7241ВС9</t>
+  </si>
+  <si>
+    <t>2П7240ВС9</t>
+  </si>
+  <si>
+    <t>4320.8-А</t>
+  </si>
+  <si>
+    <t>2П7240ВС9 4320.8-А</t>
+  </si>
+  <si>
+    <t>АЕЯР.432140.605ТУ</t>
+  </si>
+  <si>
+    <t>2П7241ВС9 4320.8-А</t>
+  </si>
+  <si>
+    <t>2П767А9</t>
+  </si>
+  <si>
+    <t>КТ-89</t>
+  </si>
+  <si>
+    <t>2П767А9 КТ-89</t>
+  </si>
+  <si>
+    <t>TO-252</t>
   </si>
 </sst>
 </file>
@@ -482,7 +525,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -497,6 +540,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="21">
     <cellStyle name="Accent 1 1" xfId="3" xr:uid="{59C07D72-8E19-46CF-887A-3117F6F3785F}"/>
@@ -831,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A86DCBB-C7F7-4A7A-A3DD-2292F908D4B3}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -842,7 +886,7 @@
     <col min="6" max="7" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -868,7 +912,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -891,7 +935,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -914,7 +958,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -937,7 +981,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>23</v>
       </c>
@@ -960,7 +1004,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -984,7 +1028,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1008,7 +1052,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>35</v>
       </c>
@@ -1031,7 +1075,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
@@ -1054,7 +1098,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
@@ -1077,7 +1121,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -1100,7 +1144,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -1123,7 +1167,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>77</v>
       </c>
@@ -1145,6 +1189,81 @@
       <c r="G13" t="s">
         <v>47</v>
       </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1374,7 +1493,28 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G10" s="3"/>
+      <c r="A10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" t="s">
+        <v>87</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5009AFC0-E8F3-46FA-A787-DD981AB783EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D645A082-CF2A-4ED0-8D9D-CBA08D2466E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="1770" windowWidth="23085" windowHeight="13635" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="nmos" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="97">
   <si>
     <t>Part Number</t>
   </si>
@@ -317,6 +317,18 @@
   </si>
   <si>
     <t>TO-252</t>
+  </si>
+  <si>
+    <t>NPN 1B2C3E IGBT</t>
+  </si>
+  <si>
+    <t>2Е725Б</t>
+  </si>
+  <si>
+    <t>КТ-43А-1.01</t>
+  </si>
+  <si>
+    <t>АЕЯР.432140.492ТУ</t>
   </si>
 </sst>
 </file>
@@ -1259,7 +1271,7 @@
         <v>92</v>
       </c>
       <c r="G16" s="2"/>
-      <c r="H16" s="6" t="s">
+      <c r="H16" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="2"/>
@@ -1523,14 +1535,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E342F99-7B21-453C-995C-4446AFFB9290}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1580,6 +1594,29 @@
       </c>
       <c r="G2" s="2" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D645A082-CF2A-4ED0-8D9D-CBA08D2466E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3FD59D-5217-459A-8C67-6345E2AB2B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="23085" windowHeight="13635" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="nmos" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="97">
   <si>
     <t>Part Number</t>
   </si>
@@ -537,7 +537,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -552,7 +552,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="21">
     <cellStyle name="Accent 1 1" xfId="3" xr:uid="{59C07D72-8E19-46CF-887A-3117F6F3785F}"/>
@@ -1218,7 +1217,9 @@
       <c r="E14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
         <v>82</v>
@@ -1600,7 +1601,7 @@
       <c r="A3" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" t="s">
         <v>95</v>
       </c>
       <c r="C3" t="s">
@@ -1615,7 +1616,7 @@
       <c r="F3" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" t="s">
         <v>96</v>
       </c>
     </row>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3FD59D-5217-459A-8C67-6345E2AB2B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D279250B-3738-4C4F-B427-2041CE654F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1425" yWindow="1425" windowWidth="23085" windowHeight="13635" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="96">
   <si>
     <t>Part Number</t>
   </si>
@@ -314,9 +314,6 @@
   </si>
   <si>
     <t>2П767А9 КТ-89</t>
-  </si>
-  <si>
-    <t>TO-252</t>
   </si>
   <si>
     <t>NPN 1B2C3E IGBT</t>
@@ -1269,7 +1266,7 @@
         <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" t="s">
@@ -1599,25 +1596,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" t="s">
         <v>94</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3" t="s">
         <v>95</v>
-      </c>
-      <c r="C3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H3" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D279250B-3738-4C4F-B427-2041CE654F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1407D5DF-6291-4F70-87D6-6D2528AAC7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="23085" windowHeight="13635" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="nmos" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="98">
   <si>
     <t>Part Number</t>
   </si>
@@ -326,6 +326,12 @@
   </si>
   <si>
     <t>АЕЯР.432140.492ТУ</t>
+  </si>
+  <si>
+    <t>BC857B</t>
+  </si>
+  <si>
+    <t>BC857B SOT23</t>
   </si>
 </sst>
 </file>
@@ -1624,7 +1630,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99D7E81C-1413-426F-8EBE-717C09928723}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -1683,6 +1689,29 @@
         <v>37</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1407D5DF-6291-4F70-87D6-6D2528AAC7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36B8567-C4B5-4263-8856-158F16DAF686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="nmos" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="101">
   <si>
     <t>Part Number</t>
   </si>
@@ -332,6 +332,15 @@
   </si>
   <si>
     <t>BC857B SOT23</t>
+  </si>
+  <si>
+    <t>FCA47N60</t>
+  </si>
+  <si>
+    <t>TO-3PN</t>
+  </si>
+  <si>
+    <t>FCA47N60 TO-3PN</t>
   </si>
 </sst>
 </file>
@@ -540,16 +549,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -889,7 +895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A86DCBB-C7F7-4A7A-A3DD-2292F908D4B3}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -927,19 +933,19 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -948,6 +954,9 @@
       <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -971,6 +980,9 @@
       <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -991,12 +1003,15 @@
       <c r="F4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1014,21 +1029,24 @@
       <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -1038,21 +1056,23 @@
         <v>31</v>
       </c>
       <c r="G6" s="2"/>
-      <c r="H6" t="s">
+      <c r="H6" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -1062,9 +1082,11 @@
         <v>31</v>
       </c>
       <c r="G7" s="2"/>
-      <c r="H7" t="s">
+      <c r="H7" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
@@ -1085,9 +1107,12 @@
       <c r="F8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -1111,6 +1136,9 @@
       <c r="G9" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
@@ -1134,9 +1162,12 @@
       <c r="G10" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1145,30 +1176,33 @@
       <c r="C11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -1180,29 +1214,35 @@
       <c r="G12" s="2" t="s">
         <v>74</v>
       </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1249,6 +1289,7 @@
       <c r="F15" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
         <v>87</v>
       </c>
@@ -1256,30 +1297,80 @@
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="2" t="s">
         <v>39</v>
       </c>
       <c r="G16" s="2"/>
-      <c r="H16" t="s">
+      <c r="H16" s="2" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1578,16 +1669,16 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1667,16 +1758,16 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36B8567-C4B5-4263-8856-158F16DAF686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED59BE7E-2874-4BD3-8B1C-F81E4E4DE538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="99">
   <si>
     <t>Part Number</t>
   </si>
@@ -177,9 +177,6 @@
     <t>TO-220</t>
   </si>
   <si>
-    <t>STP24NF10 TO-220</t>
-  </si>
-  <si>
     <t>STMicroelectronics</t>
   </si>
   <si>
@@ -268,12 +265,6 @@
   </si>
   <si>
     <t>AO3401A SOT23</t>
-  </si>
-  <si>
-    <t>STB24NF10</t>
-  </si>
-  <si>
-    <t>STB24NF10  TO-263-2</t>
   </si>
   <si>
     <t>2П795А92</t>
@@ -341,6 +332,9 @@
   </si>
   <si>
     <t>FCA47N60 TO-3PN</t>
+  </si>
+  <si>
+    <t>Footprint Ref 2</t>
   </si>
 </sst>
 </file>
@@ -895,7 +889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A86DCBB-C7F7-4A7A-A3DD-2292F908D4B3}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -903,10 +897,10 @@
     <col min="3" max="3" width="22.140625" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="22.42578125" customWidth="1"/>
-    <col min="6" max="7" width="16.5703125" customWidth="1"/>
+    <col min="6" max="8" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -926,13 +920,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -951,14 +948,15 @@
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -977,14 +975,15 @@
       <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -1003,14 +1002,15 @@
       <c r="F4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1029,14 +1029,15 @@
       <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -1056,13 +1057,14 @@
         <v>31</v>
       </c>
       <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="2"/>
       <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>33</v>
       </c>
@@ -1082,13 +1084,14 @@
         <v>31</v>
       </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>35</v>
       </c>
@@ -1107,14 +1110,15 @@
       <c r="F8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
@@ -1133,14 +1137,15 @@
       <c r="F9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
@@ -1159,22 +1164,21 @@
       <c r="F10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>44</v>
@@ -1186,24 +1190,27 @@
         <v>45</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
@@ -1211,144 +1218,136 @@
       <c r="F12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="G15" s="2"/>
-      <c r="H15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1359,18 +1358,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="K18" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1417,19 +1405,19 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>9</v>
@@ -1440,19 +1428,19 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>21</v>
@@ -1463,19 +1451,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>24</v>
@@ -1486,19 +1474,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>24</v>
@@ -1509,19 +1497,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>39</v>
@@ -1532,19 +1520,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>39</v>
@@ -1555,19 +1543,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>39</v>
@@ -1578,19 +1566,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>24</v>
@@ -1601,26 +1589,26 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1670,48 +1658,48 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" t="s">
         <v>92</v>
-      </c>
-      <c r="F3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H3" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1759,19 +1747,19 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>24</v>
@@ -1782,19 +1770,19 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>24</v>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED59BE7E-2874-4BD3-8B1C-F81E4E4DE538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD36A49-FEB1-4BA7-A16A-620F9858C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="101">
   <si>
     <t>Part Number</t>
   </si>
@@ -335,6 +335,12 @@
   </si>
   <si>
     <t>Footprint Ref 2</t>
+  </si>
+  <si>
+    <t>Si4840BDY</t>
+  </si>
+  <si>
+    <t>Si4840BDY 8-SOIC</t>
   </si>
 </sst>
 </file>
@@ -1335,14 +1341,28 @@
       <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD36A49-FEB1-4BA7-A16A-620F9858C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30061CF-4040-9946-BA05-42EED692EEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="nmos" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="104">
   <si>
     <t>Part Number</t>
   </si>
@@ -96,9 +96,6 @@
     <t>SOT-323</t>
   </si>
   <si>
-    <t>BSS138W-7-F SOT323</t>
-  </si>
-  <si>
     <t>N-Channel 1G3D2S</t>
   </si>
   <si>
@@ -187,9 +184,6 @@
   </si>
   <si>
     <t>BSS84W-7-F</t>
-  </si>
-  <si>
-    <t>BSS84W-7-F SOT323</t>
   </si>
   <si>
     <t>P-Channel 1G3D2S</t>
@@ -340,7 +334,22 @@
     <t>Si4840BDY</t>
   </si>
   <si>
-    <t>Si4840BDY 8-SOIC</t>
+    <t>TO-3PN_Horizontal</t>
+  </si>
+  <si>
+    <t>BSS138W-7-F SOT-323</t>
+  </si>
+  <si>
+    <t>Si4840BDY SOIC-8</t>
+  </si>
+  <si>
+    <t>SOIC-8</t>
+  </si>
+  <si>
+    <t>BSS84W-7-F SOT-323</t>
+  </si>
+  <si>
+    <t>2Е725Б КТ-43А-1.01</t>
   </si>
 </sst>
 </file>
@@ -563,6 +572,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="21">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="2" xr:uid="{5A4A247A-9E13-45F7-8C42-156984DFCA88}"/>
     <cellStyle name="Accent 1 1" xfId="3" xr:uid="{59C07D72-8E19-46CF-887A-3117F6F3785F}"/>
     <cellStyle name="Accent 2 1" xfId="4" xr:uid="{6BABBE6D-B89F-40A5-B377-65A1ECF4F8D6}"/>
     <cellStyle name="Accent 3 1" xfId="5" xr:uid="{4C06F33B-F628-495C-9BA2-60FAC1B8690A}"/>
@@ -582,8 +593,6 @@
     <cellStyle name="Status 1" xfId="17" xr:uid="{B5CEB193-82F1-4869-9033-6CA5CF994AD1}"/>
     <cellStyle name="Text 1" xfId="18" xr:uid="{82FD0F21-4428-49B3-91A7-88A1E12D7A17}"/>
     <cellStyle name="Warning 1" xfId="19" xr:uid="{C0F92B33-BA6B-43EB-9AF1-3DB4037EF412}"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="2" xr:uid="{5A4A247A-9E13-45F7-8C42-156984DFCA88}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -599,9 +608,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -639,7 +648,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -745,7 +754,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -887,7 +896,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -896,17 +905,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A86DCBB-C7F7-4A7A-A3DD-2292F908D4B3}">
   <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" customWidth="1"/>
-    <col min="6" max="8" width="16.5703125" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="9" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -926,7 +932,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -935,7 +941,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -962,7 +968,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -989,7 +995,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -997,280 +1003,280 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>12</v>
@@ -1281,56 +1287,56 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
@@ -1340,34 +1346,34 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1388,16 +1394,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A36DDB-75CB-4526-8B7C-3E1D54E638B5}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="7" width="16.5703125" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="9" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1423,21 +1427,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>9</v>
@@ -1446,189 +1450,189 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1639,18 +1643,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E342F99-7B21-453C-995C-4446AFFB9290}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="22.28515625" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="9" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1676,50 +1676,50 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" t="s">
         <v>90</v>
-      </c>
-      <c r="B3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1730,16 +1730,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99D7E81C-1413-426F-8EBE-717C09928723}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="7" width="16.5703125" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="9" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1765,50 +1763,50 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" t="s">
-        <v>70</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30061CF-4040-9946-BA05-42EED692EEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF192810-8AB3-457B-A322-0C29D1FB205C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="29895" yWindow="1095" windowWidth="21600" windowHeight="11385" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="nmos" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="123">
   <si>
     <t>Part Number</t>
   </si>
@@ -350,13 +350,96 @@
   </si>
   <si>
     <t>2Е725Б КТ-43А-1.01</t>
+  </si>
+  <si>
+    <t>IRFP450</t>
+  </si>
+  <si>
+    <t>TO-3PN_Vertical</t>
+  </si>
+  <si>
+    <t>TO-247</t>
+  </si>
+  <si>
+    <t>IRFP450 TO-247</t>
+  </si>
+  <si>
+    <t>ONS</t>
+  </si>
+  <si>
+    <r>
+      <t>FGH40N60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SFD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FGH40N60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SFD TO-247</t>
+    </r>
+  </si>
+  <si>
+    <t>Dual n-mos 8-soic</t>
+  </si>
+  <si>
+    <t>IRF7380</t>
+  </si>
+  <si>
+    <t>IRF7380 8-SOIC</t>
+  </si>
+  <si>
+    <t>INFIN</t>
+  </si>
+  <si>
+    <t>WMT04N10TS</t>
+  </si>
+  <si>
+    <t>SOT223</t>
+  </si>
+  <si>
+    <t>WMT04N10TS SOT223</t>
+  </si>
+  <si>
+    <t>WAYON</t>
+  </si>
+  <si>
+    <t>P-Channel 1G24D3S</t>
+  </si>
+  <si>
+    <t>IRF7380TRPBF</t>
+  </si>
+  <si>
+    <t>IRFR120NTRPBF</t>
+  </si>
+  <si>
+    <t>IRFR120NTRPBF TO-252-2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -460,6 +543,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -558,7 +649,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -570,10 +661,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="21">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="2" xr:uid="{5A4A247A-9E13-45F7-8C42-156984DFCA88}"/>
     <cellStyle name="Accent 1 1" xfId="3" xr:uid="{59C07D72-8E19-46CF-887A-3117F6F3785F}"/>
     <cellStyle name="Accent 2 1" xfId="4" xr:uid="{6BABBE6D-B89F-40A5-B377-65A1ECF4F8D6}"/>
     <cellStyle name="Accent 3 1" xfId="5" xr:uid="{4C06F33B-F628-495C-9BA2-60FAC1B8690A}"/>
@@ -593,6 +685,8 @@
     <cellStyle name="Status 1" xfId="17" xr:uid="{B5CEB193-82F1-4869-9033-6CA5CF994AD1}"/>
     <cellStyle name="Text 1" xfId="18" xr:uid="{82FD0F21-4428-49B3-91A7-88A1E12D7A17}"/>
     <cellStyle name="Warning 1" xfId="19" xr:uid="{C0F92B33-BA6B-43EB-9AF1-3DB4037EF412}"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="2" xr:uid="{5A4A247A-9E13-45F7-8C42-156984DFCA88}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -608,9 +702,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -648,7 +742,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -754,7 +848,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -896,7 +990,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -904,15 +998,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A86DCBB-C7F7-4A7A-A3DD-2292F908D4B3}">
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="9" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="9" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -941,7 +1035,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -968,7 +1062,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -995,7 +1089,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -1022,7 +1116,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -1049,7 +1143,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -1076,7 +1170,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -1103,7 +1197,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -1130,7 +1224,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
@@ -1157,7 +1251,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
@@ -1184,7 +1278,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -1211,7 +1305,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>69</v>
       </c>
@@ -1238,7 +1332,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>74</v>
       </c>
@@ -1265,115 +1359,735 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
       <c r="I14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
       <c r="I15" s="2" t="s">
         <v>31</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="s">
+      <c r="G16" s="5"/>
+      <c r="H16" s="5" t="s">
         <v>11</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2" t="s">
+      <c r="G17" s="5"/>
+      <c r="H17" s="5" t="s">
         <v>25</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A36DDB-75CB-4526-8B7C-3E1D54E638B5}">
+  <dimension ref="A1:M22"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="9" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1385,255 +2099,68 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A36DDB-75CB-4526-8B7C-3E1D54E638B5}">
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="9" width="20.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" t="s">
-        <v>82</v>
-      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1642,15 +2169,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E342F99-7B21-453C-995C-4446AFFB9290}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="9" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="9" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1676,7 +2203,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>61</v>
       </c>
@@ -1699,7 +2226,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>88</v>
       </c>
@@ -1720,6 +2247,29 @@
       </c>
       <c r="H3" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1730,14 +2280,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99D7E81C-1413-426F-8EBE-717C09928723}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="9" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="9" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1763,7 +2313,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>66</v>
       </c>
@@ -1786,7 +2336,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>91</v>
       </c>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF192810-8AB3-457B-A322-0C29D1FB205C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE465AC-ADEB-414B-BFD5-1FD24418CDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29895" yWindow="1095" windowWidth="21600" windowHeight="11385" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="126">
   <si>
     <t>Part Number</t>
   </si>
@@ -433,6 +433,15 @@
   </si>
   <si>
     <t>IRFR120NTRPBF TO-252-2</t>
+  </si>
+  <si>
+    <t>HOTTECH5N10</t>
+  </si>
+  <si>
+    <t>5N10</t>
+  </si>
+  <si>
+    <t>5N10 SOT23</t>
   </si>
 </sst>
 </file>
@@ -649,7 +658,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -659,9 +668,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1360,26 +1366,26 @@
       <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
         <v>82</v>
       </c>
@@ -1387,26 +1393,26 @@
       <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
         <v>31</v>
       </c>
@@ -1414,26 +1420,26 @@
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
+      <c r="G16" s="2"/>
+      <c r="H16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I16" s="2"/>
@@ -1441,26 +1447,26 @@
       <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5" t="s">
+      <c r="G17" s="2"/>
+      <c r="H17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="I17" s="2"/>
@@ -1468,26 +1474,26 @@
       <c r="K17" s="2"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5" t="s">
+      <c r="G18" s="2"/>
+      <c r="H18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="I18" s="2"/>
@@ -1495,78 +1501,92 @@
       <c r="K18" s="2"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5" t="s">
+      <c r="G19" s="2"/>
+      <c r="H19" s="2" t="s">
         <v>114</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5" t="s">
+      <c r="G20" s="2"/>
+      <c r="H20" s="2" t="s">
         <v>114</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="A21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE465AC-ADEB-414B-BFD5-1FD24418CDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19D1839-04CD-4182-8FB2-6BF8C5CD7C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29895" yWindow="1095" windowWidth="21600" windowHeight="11385" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="nmos" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="128">
   <si>
     <t>Part Number</t>
   </si>
@@ -442,6 +442,12 @@
   </si>
   <si>
     <t>5N10 SOT23</t>
+  </si>
+  <si>
+    <t>IRFR9120</t>
+  </si>
+  <si>
+    <t>IRFR9120 TO-252-2</t>
   </si>
 </sst>
 </file>
@@ -2018,13 +2024,27 @@
       <c r="M11" s="2"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19D1839-04CD-4182-8FB2-6BF8C5CD7C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6467C94-4886-4C4F-A6C5-A419879348CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="nmos" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="130">
   <si>
     <t>Part Number</t>
   </si>
@@ -448,6 +448,12 @@
   </si>
   <si>
     <t>IRFR9120 TO-252-2</t>
+  </si>
+  <si>
+    <t>IRFR220</t>
+  </si>
+  <si>
+    <t>IRFR220 TO-252-2</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A86DCBB-C7F7-4A7A-A3DD-2292F908D4B3}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
@@ -1585,14 +1591,28 @@
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="A22" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
@@ -1691,6 +1711,17 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6467C94-4886-4C4F-A6C5-A419879348CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039495C0-C948-4384-AB34-B52A0FF16BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="nmos" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="105">
   <si>
     <t>Part Number</t>
   </si>
@@ -69,9 +69,6 @@
     <t>SuperSOT6</t>
   </si>
   <si>
-    <t>FDC655BN SuperSOT6</t>
-  </si>
-  <si>
     <t>Fairchild semiconductor</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
     <t>SO-8</t>
   </si>
   <si>
-    <t>IRF9910PBF SO-8</t>
-  </si>
-  <si>
     <t>8-SOIC</t>
   </si>
   <si>
@@ -111,9 +105,6 @@
     <t>SOT23</t>
   </si>
   <si>
-    <t>SI2302CDS-T1-GE3 SOT23</t>
-  </si>
-  <si>
     <t>Vishay</t>
   </si>
   <si>
@@ -123,9 +114,6 @@
     <t>КТ-90</t>
   </si>
   <si>
-    <t>2П769Д91 КТ-90</t>
-  </si>
-  <si>
     <t>N-Channel 1G2D3S</t>
   </si>
   <si>
@@ -138,15 +126,9 @@
     <t>2П769В91</t>
   </si>
   <si>
-    <t>2П769В91 КТ-90</t>
-  </si>
-  <si>
     <t>IRLML2502</t>
   </si>
   <si>
-    <t>IRLML2502 SOT23</t>
-  </si>
-  <si>
     <t>UMW</t>
   </si>
   <si>
@@ -156,18 +138,12 @@
     <t>TO-252-2</t>
   </si>
   <si>
-    <t>NCE4060K TO-252-2</t>
-  </si>
-  <si>
     <t>NCE Power</t>
   </si>
   <si>
     <t>IRFR1205TR</t>
   </si>
   <si>
-    <t>IRFR1205TR TO-252-2</t>
-  </si>
-  <si>
     <t>STP24NF10</t>
   </si>
   <si>
@@ -180,9 +156,6 @@
     <t>FDC654P</t>
   </si>
   <si>
-    <t>FDC654P SuperSOT6</t>
-  </si>
-  <si>
     <t>BSS84W-7-F</t>
   </si>
   <si>
@@ -192,36 +165,21 @@
     <t>SI2301CDS-T1-GE3</t>
   </si>
   <si>
-    <t>SI2301CDS-T1-GE3 SOT23</t>
-  </si>
-  <si>
     <t>IRLML6402</t>
   </si>
   <si>
-    <t>IRLML6402 SOT23</t>
-  </si>
-  <si>
     <t>NCE40P40K</t>
   </si>
   <si>
-    <t>NCE40P40K TO-252-2</t>
-  </si>
-  <si>
     <t>P-Channel 1G2D3S</t>
   </si>
   <si>
     <t>FDD6685</t>
   </si>
   <si>
-    <t>FDD6685 TO-252-2</t>
-  </si>
-  <si>
     <t>AOD403</t>
   </si>
   <si>
-    <t>AOD403 TO-252-2</t>
-  </si>
-  <si>
     <t>BC847</t>
   </si>
   <si>
@@ -249,22 +207,13 @@
     <t>AO3400</t>
   </si>
   <si>
-    <t>AO3400 SOT23</t>
-  </si>
-  <si>
     <t>Hottech Semiconductor</t>
   </si>
   <si>
     <t>AO3401A</t>
   </si>
   <si>
-    <t>AO3401A SOT23</t>
-  </si>
-  <si>
     <t>2П795А92</t>
-  </si>
-  <si>
-    <t>2П795А92 КТ-94</t>
   </si>
   <si>
     <t>КТ-94</t>
@@ -283,24 +232,15 @@
     <t>4320.8-А</t>
   </si>
   <si>
-    <t>2П7240ВС9 4320.8-А</t>
-  </si>
-  <si>
     <t>АЕЯР.432140.605ТУ</t>
   </si>
   <si>
-    <t>2П7241ВС9 4320.8-А</t>
-  </si>
-  <si>
     <t>2П767А9</t>
   </si>
   <si>
     <t>КТ-89</t>
   </si>
   <si>
-    <t>2П767А9 КТ-89</t>
-  </si>
-  <si>
     <t>NPN 1B2C3E IGBT</t>
   </si>
   <si>
@@ -325,9 +265,6 @@
     <t>TO-3PN</t>
   </si>
   <si>
-    <t>FCA47N60 TO-3PN</t>
-  </si>
-  <si>
     <t>Footprint Ref 2</t>
   </si>
   <si>
@@ -337,18 +274,9 @@
     <t>TO-3PN_Horizontal</t>
   </si>
   <si>
-    <t>BSS138W-7-F SOT-323</t>
-  </si>
-  <si>
-    <t>Si4840BDY SOIC-8</t>
-  </si>
-  <si>
     <t>SOIC-8</t>
   </si>
   <si>
-    <t>BSS84W-7-F SOT-323</t>
-  </si>
-  <si>
     <t>2Е725Б КТ-43А-1.01</t>
   </si>
   <si>
@@ -359,12 +287,6 @@
   </si>
   <si>
     <t>TO-247</t>
-  </si>
-  <si>
-    <t>IRFP450 TO-247</t>
-  </si>
-  <si>
-    <t>ONS</t>
   </si>
   <si>
     <r>
@@ -405,9 +327,6 @@
     <t>IRF7380</t>
   </si>
   <si>
-    <t>IRF7380 8-SOIC</t>
-  </si>
-  <si>
     <t>INFIN</t>
   </si>
   <si>
@@ -417,9 +336,6 @@
     <t>SOT223</t>
   </si>
   <si>
-    <t>WMT04N10TS SOT223</t>
-  </si>
-  <si>
     <t>WAYON</t>
   </si>
   <si>
@@ -432,28 +348,37 @@
     <t>IRFR120NTRPBF</t>
   </si>
   <si>
-    <t>IRFR120NTRPBF TO-252-2</t>
-  </si>
-  <si>
     <t>HOTTECH5N10</t>
   </si>
   <si>
     <t>5N10</t>
   </si>
   <si>
-    <t>5N10 SOT23</t>
-  </si>
-  <si>
     <t>IRFR9120</t>
   </si>
   <si>
-    <t>IRFR9120 TO-252-2</t>
-  </si>
-  <si>
     <t>IRFR220</t>
   </si>
   <si>
-    <t>IRFR220 TO-252-2</t>
+    <t>IRFR220PbF</t>
+  </si>
+  <si>
+    <t>NDS9948</t>
+  </si>
+  <si>
+    <t>ON Semiconductor</t>
+  </si>
+  <si>
+    <t>FGH60N60SMD</t>
+  </si>
+  <si>
+    <t>Infineon Technologies</t>
+  </si>
+  <si>
+    <t>IRLML2060TRPBF</t>
+  </si>
+  <si>
+    <t>IRLML2060</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +969,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -1060,8 +985,9 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
+      <c r="C2" s="2" t="str">
+        <f t="shared" ref="C2:C21" si="0">_xlfn.CONCAT(D2, " ", B2)</f>
+        <v>FDC655BN SuperSOT6</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -1074,7 +1000,7 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -1082,26 +1008,27 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IRF9910PBF SO-8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -1109,26 +1036,27 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>BSS138W-7-F SOT-323</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -1136,26 +1064,27 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SI2302CDS-T1-GE3 SOT23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -1163,80 +1092,83 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2П769Д91 КТ-90</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2П769В91 КТ-90</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IRLML2502 SOT23</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -1244,26 +1176,27 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>NCE4060K TO-252-2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -1271,26 +1204,27 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IRFR1205TR TO-252-2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -1298,26 +1232,27 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="2" t="s">
-        <v>43</v>
+      <c r="C11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">STP24NF10 </v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -1325,26 +1260,27 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>21</v>
+      </c>
+      <c r="C12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>AO3400 SOT23</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1352,107 +1288,111 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>75</v>
+        <v>59</v>
+      </c>
+      <c r="C13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2П795А92 КТ-94</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>81</v>
+        <v>63</v>
+      </c>
+      <c r="C14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2П7240ВС9 4320.8-А</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>86</v>
+        <v>66</v>
+      </c>
+      <c r="C15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2П767А9 КТ-89</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>95</v>
+        <v>74</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>FCA47N60 TO-3PN</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -1460,26 +1400,27 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>100</v>
+        <v>78</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Si4840BDY SOIC-8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -1487,26 +1428,27 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>107</v>
+        <v>82</v>
+      </c>
+      <c r="C18" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IRFP450 TO-247</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -1514,117 +1456,136 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>113</v>
+        <v>13</v>
+      </c>
+      <c r="C19" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IRF7380 8-SOIC</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>122</v>
+        <v>32</v>
+      </c>
+      <c r="C20" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IRFR120NTRPBF TO-252-2</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>125</v>
+        <v>21</v>
+      </c>
+      <c r="C21" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>5N10 SOT23</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>129</v>
+        <v>32</v>
+      </c>
+      <c r="C22" s="2" t="str">
+        <f>_xlfn.CONCAT(D22, " ", B22)</f>
+        <v>IRFR220PbF TO-252-2</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="2" t="str">
+        <f>_xlfn.CONCAT(D23, " ", B23)</f>
+        <v>IRLML2060TRPBF SOT23</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="H23" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
@@ -1766,25 +1727,26 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>47</v>
+      <c r="C2" s="2" t="str">
+        <f t="shared" ref="C2:C12" si="0">_xlfn.CONCAT(D2, " ", B2)</f>
+        <v>FDC654P SuperSOT6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -1795,25 +1757,26 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>BSS84W-7-F SOT-323</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -1824,25 +1787,26 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>51</v>
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>SI2301CDS-T1-GE3 SOT23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -1853,25 +1817,26 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>53</v>
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IRLML6402 SOT23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -1882,25 +1847,26 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>55</v>
+        <v>32</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>NCE40P40K TO-252-2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -1911,25 +1877,26 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>58</v>
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>FDD6685 TO-252-2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -1940,25 +1907,26 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>60</v>
+        <v>32</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>AOD403 TO-252-2</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -1969,25 +1937,26 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>21</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>AO3401A SOT23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -1998,26 +1967,27 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>83</v>
+        <v>63</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2П7241ВС9 4320.8-А</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -2027,25 +1997,26 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="C11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>WMT04N10TS SOT223</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -2056,25 +2027,26 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>127</v>
+        <v>32</v>
+      </c>
+      <c r="C12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>IRFR9120 TO-252-2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -2084,13 +2056,28 @@
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="A13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="str">
+        <f>_xlfn.CONCAT(D13, " ", B13)</f>
+        <v>NDS9948 8-SOIC</v>
+      </c>
+      <c r="D13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -2240,7 +2227,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E342F99-7B21-453C-995C-4446AFFB9290}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
@@ -2276,71 +2263,95 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s">
-        <v>108</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="str">
+        <f>_xlfn.CONCAT(D5, " ", B5)</f>
+        <v>FGH60N60SMD TO-247</v>
+      </c>
+      <c r="D5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2386,48 +2397,48 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/library/transistors.xlsx
+++ b/library/transistors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039495C0-C948-4384-AB34-B52A0FF16BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4F7B6D-02C6-4A3B-84F5-8A0274F0988B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="105">
   <si>
     <t>Part Number</t>
   </si>
@@ -1388,9 +1388,11 @@
         <v>25</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
         <v>10</v>
       </c>
@@ -1446,7 +1448,9 @@
       <c r="F18" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="H18" s="2" t="s">
         <v>22</v>
       </c>
@@ -2227,15 +2231,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E342F99-7B21-453C-995C-4446AFFB9290}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
     <col min="3" max="3" width="25.85546875" customWidth="1"/>
-    <col min="4" max="9" width="20.85546875" customWidth="1"/>
+    <col min="4" max="10" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2255,13 +2259,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>47</v>
       </c>
@@ -2280,11 +2287,12 @@
       <c r="F2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>68</v>
       </c>
@@ -2303,11 +2311,11 @@
       <c r="F3" t="s">
         <v>68</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>83</v>
       </c>
@@ -2327,10 +2335,13 @@
         <v>81</v>
       </c>
       <c r="G4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>101</v>
       </c>
@@ -2351,6 +2362,9 @@
         <v>81</v>
       </c>
       <c r="G5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" t="s">
         <v>100</v>
       </c>
     </row>
